--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488217_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488217_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9781</v>
+        <v>4.7828</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1519</v>
+        <v>3.8581</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8262</v>
+        <v>0.9247</v>
       </c>
       <c r="G2" t="n">
         <v>1.7873</v>
@@ -610,13 +610,13 @@
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0197</v>
+        <v>-0.1756</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0584</v>
+        <v>-0.3522</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0781</v>
+        <v>0.1766</v>
       </c>
       <c r="V2" t="n">
         <v>1.133</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>X. NEWSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6838</v>
+        <v>2.8386</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3036</v>
+        <v>-0.024</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9874</v>
+        <v>2.8626</v>
       </c>
       <c r="G3" t="n">
-        <v>3.62</v>
+        <v>-1.9326</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0056</v>
+        <v>0.0412</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6145</v>
+        <v>-1.9738</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2877</v>
+        <v>-2.0612</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5412</v>
+        <v>0.3429</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7465000000000001</v>
+        <v>-2.4041</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3323</v>
+        <v>0.1286</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4643</v>
+        <v>-0.3017</v>
       </c>
       <c r="O3" t="n">
-        <v>0.868</v>
+        <v>0.4303</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.7793</v>
+        <v>1.297</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9264</v>
+        <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1575</v>
+        <v>0.0115</v>
       </c>
       <c r="T3" t="n">
-        <v>0.485</v>
+        <v>-0.8129</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6725</v>
+        <v>0.8244</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3144</v>
+        <v>3.4627</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6294</v>
+        <v>3.7766</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9439</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. NEWSON</t>
+          <t>P. VILLAREJO CALATAYUD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5426</v>
+        <v>1.9373</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07389999999999999</v>
+        <v>-1.889</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4687</v>
+        <v>3.8263</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.9326</v>
+        <v>2.0071</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0412</v>
+        <v>0.9859</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.9738</v>
+        <v>1.0212</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.0612</v>
+        <v>1.9102</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3429</v>
+        <v>0.6435</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.4041</v>
+        <v>1.2667</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1286</v>
+        <v>0.0969</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3017</v>
+        <v>0.3425</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4303</v>
+        <v>-0.2456</v>
       </c>
       <c r="P4" t="n">
-        <v>1.297</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2234</v>
+        <v>2.4087</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2845</v>
+        <v>0.1122</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.715</v>
+        <v>-1.0194</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4305</v>
+        <v>1.1316</v>
       </c>
       <c r="V4" t="n">
-        <v>3.4627</v>
+        <v>0.1886</v>
       </c>
       <c r="W4" t="n">
-        <v>3.7766</v>
+        <v>-0.0005</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3139</v>
+        <v>0.1891</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. VILLAREJO CALATAYUD</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.136</v>
+        <v>1.2848</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1828</v>
+        <v>-1.087</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3188</v>
+        <v>2.3719</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0071</v>
+        <v>3.62</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9859</v>
+        <v>2.0056</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0212</v>
+        <v>1.6145</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9102</v>
+        <v>2.2877</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6435</v>
+        <v>1.5412</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2667</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0969</v>
+        <v>1.3323</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3425</v>
+        <v>0.4643</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2456</v>
+        <v>0.868</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3706</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7793</v>
+        <v>-3.7057</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4087</v>
+        <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3109</v>
+        <v>0.7585</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3132</v>
+        <v>-0.2984</v>
       </c>
       <c r="U5" t="n">
-        <v>1.624</v>
+        <v>1.057</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1886</v>
+        <v>-0.3144</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0005</v>
+        <v>0.6294</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1891</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9861</v>
+        <v>1.1321</v>
       </c>
       <c r="E6" t="n">
-        <v>0.106</v>
+        <v>0.3998</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8801</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-1.5671</v>
@@ -922,13 +922,13 @@
         <v>2.2234</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1743</v>
+        <v>-0.0283</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.766</v>
+        <v>-0.4722</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5917</v>
+        <v>0.4439</v>
       </c>
       <c r="V6" t="n">
         <v>0.5041</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0897</v>
+        <v>0.679</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5467</v>
+        <v>-2.2529</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6365</v>
+        <v>2.9319</v>
       </c>
       <c r="G7" t="n">
         <v>3.2449</v>
@@ -1000,13 +1000,13 @@
         <v>1.8529</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7083</v>
+        <v>-0.1191</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2037</v>
+        <v>-0.9099</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4954</v>
+        <v>0.7909</v>
       </c>
       <c r="V7" t="n">
         <v>1.2589</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.819</v>
+        <v>-0.2543</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1739</v>
+        <v>0.4677</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9928</v>
+        <v>-0.722</v>
       </c>
       <c r="G8" t="n">
         <v>1.8722</v>
@@ -1078,13 +1078,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1353</v>
+        <v>0.4293</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6019</v>
+        <v>-0.3081</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4666</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2589</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>U. FRISCIA PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5228</v>
+        <v>-1.2581</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2468</v>
+        <v>-2.0313</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.276</v>
+        <v>0.7732</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3184</v>
+        <v>0.514</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5871</v>
+        <v>-0.3401</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2688</v>
+        <v>0.8541</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1303</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7003</v>
+        <v>-0.8334</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5699</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8120000000000001</v>
+        <v>0.6009</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1131</v>
+        <v>0.4933</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6989</v>
+        <v>0.1076</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6676</v>
+        <v>1.8529</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3589</v>
+        <v>-0.3874</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1057</v>
+        <v>-0.406</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2532</v>
+        <v>0.0186</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.0147</v>
+        <v>-1.3847</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3847</v>
+        <v>-1.6992</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. FRISCIA PEREZ</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7002</v>
+        <v>-1.7679</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2272</v>
+        <v>-1.4426</v>
       </c>
       <c r="F10" t="n">
-        <v>0.527</v>
+        <v>-0.3252</v>
       </c>
       <c r="G10" t="n">
-        <v>0.514</v>
+        <v>0.3184</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3401</v>
+        <v>1.5871</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8541</v>
+        <v>-1.2688</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.08690000000000001</v>
+        <v>1.1303</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8334</v>
+        <v>1.7003</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7465000000000001</v>
+        <v>-0.5699</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6009</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4933</v>
+        <v>-0.1131</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1076</v>
+        <v>-0.6989</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8294</v>
+        <v>0.1138</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6019</v>
+        <v>-0.0901</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2276</v>
+        <v>0.2039</v>
       </c>
       <c r="V10" t="n">
+        <v>-2.0147</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="X10" t="n">
         <v>-1.3847</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.3144</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-1.6992</v>
       </c>
     </row>
     <row r="11">
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.374300000000002</v>
+        <v>9.374299999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.001399999999999</v>
+        <v>-4.0012</v>
       </c>
       <c r="F11" t="n">
-        <v>13.3759</v>
+        <v>13.3758</v>
       </c>
       <c r="G11" t="n">
-        <v>9.864199999999999</v>
+        <v>9.8642</v>
       </c>
       <c r="H11" t="n">
         <v>7.790699999999999</v>
@@ -1285,10 +1285,10 @@
         <v>2.0736</v>
       </c>
       <c r="J11" t="n">
-        <v>9.756699999999999</v>
+        <v>9.7567</v>
       </c>
       <c r="K11" t="n">
-        <v>7.7612</v>
+        <v>7.761200000000001</v>
       </c>
       <c r="L11" t="n">
         <v>1.9956</v>
@@ -1297,10 +1297,10 @@
         <v>0.1073999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.02950000000000008</v>
+        <v>0.0295</v>
       </c>
       <c r="O11" t="n">
-        <v>0.07790000000000005</v>
+        <v>0.07790000000000008</v>
       </c>
       <c r="P11" t="n">
         <v>-2.779300000000001</v>
@@ -1312,22 +1312,22 @@
         <v>15.7494</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7152000000000002</v>
+        <v>0.7148999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.6694</v>
+        <v>-4.6692</v>
       </c>
       <c r="U11" t="n">
-        <v>5.3844</v>
+        <v>5.384300000000001</v>
       </c>
       <c r="V11" t="n">
         <v>1.5746</v>
       </c>
       <c r="W11" t="n">
-        <v>9.439899999999998</v>
+        <v>9.4399</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.8654</v>
+        <v>-7.865400000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.0856</v>
+        <v>7.1841</v>
       </c>
       <c r="E12" t="n">
         <v>5.0544</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0311</v>
+        <v>2.1296</v>
       </c>
       <c r="G12" t="n">
         <v>2.8977</v>
@@ -1390,13 +1390,13 @@
         <v>2.2234</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0408</v>
+        <v>0.1393</v>
       </c>
       <c r="T12" t="n">
         <v>-0.715</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7558</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>3.7766</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2858</v>
+        <v>1.3843</v>
       </c>
       <c r="E13" t="n">
         <v>2.7203</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4345</v>
+        <v>-1.336</v>
       </c>
       <c r="G13" t="n">
         <v>2.206</v>
@@ -1468,13 +1468,13 @@
         <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3845</v>
+        <v>-0.286</v>
       </c>
       <c r="T13" t="n">
         <v>-0.332</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0525</v>
+        <v>0.046</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2033</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7875</v>
+        <v>0.6884</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0881</v>
+        <v>-0.9902</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8756</v>
+        <v>1.6786</v>
       </c>
       <c r="G14" t="n">
         <v>-0.8072</v>
@@ -1546,13 +1546,13 @@
         <v>1.297</v>
       </c>
       <c r="S14" t="n">
-        <v>0.483</v>
+        <v>0.3839</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4924</v>
+        <v>-0.3945</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9754</v>
+        <v>0.7784</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0061</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.336</v>
+        <v>-1.238</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3299</v>
+        <v>0.5269</v>
       </c>
       <c r="G16" t="n">
         <v>-0.182</v>
@@ -1702,13 +1702,13 @@
         <v>0.9264</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4917</v>
+        <v>-0.1968</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4924</v>
+        <v>-0.3945</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0007</v>
+        <v>0.1977</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2589</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.329</v>
+        <v>-1.1813</v>
       </c>
       <c r="E17" t="n">
         <v>-2.4229</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0938</v>
+        <v>1.2416</v>
       </c>
       <c r="G17" t="n">
         <v>-1.4583</v>
@@ -1780,13 +1780,13 @@
         <v>2.9646</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4822</v>
+        <v>-0.3345</v>
       </c>
       <c r="T17" t="n">
         <v>-0.8792</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3969</v>
+        <v>0.5446</v>
       </c>
       <c r="V17" t="n">
         <v>-0.315</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4677</v>
+        <v>-1.2707</v>
       </c>
       <c r="E18" t="n">
         <v>-1.5535</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0858</v>
+        <v>0.2827</v>
       </c>
       <c r="G18" t="n">
         <v>0.3421</v>
@@ -1858,13 +1858,13 @@
         <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-0.5011</v>
       </c>
       <c r="T18" t="n">
         <v>-0.4377</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2604</v>
+        <v>-0.0634</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0022</v>
+        <v>-1.6105</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8583</v>
+        <v>-0.4666</v>
       </c>
       <c r="F19" t="n">
         <v>-1.1439</v>
@@ -1936,10 +1936,10 @@
         <v>2.2234</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5894</v>
+        <v>-0.1977</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.149</v>
+        <v>-0.7573</v>
       </c>
       <c r="U19" t="n">
         <v>0.5596</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.48</v>
+        <v>-2.5287</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1551</v>
+        <v>-3.2531</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6752</v>
+        <v>0.7244</v>
       </c>
       <c r="G20" t="n">
         <v>-3.2025</v>
@@ -2014,13 +2014,13 @@
         <v>1.8529</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2604</v>
+        <v>0.2117</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.332</v>
+        <v>-0.4299</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5924</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>1.5738</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7414</v>
+        <v>-2.545</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3151</v>
+        <v>-2.2172</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4263</v>
+        <v>-0.3278</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9041</v>
@@ -2092,13 +2092,13 @@
         <v>0.9264</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5785</v>
+        <v>-0.3821</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.383</v>
+        <v>-0.2851</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1955</v>
+        <v>-0.097</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9589</v>
+        <v>-3.6959</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5877</v>
+        <v>-3.8815</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6287</v>
+        <v>0.1856</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5426</v>
@@ -2170,13 +2170,13 @@
         <v>1.8529</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7864</v>
+        <v>0.0494</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4414</v>
+        <v>-0.7352</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2278</v>
+        <v>0.7847</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2027</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.192</v>
+        <v>-5.732</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.478</v>
+        <v>-5.7718</v>
       </c>
       <c r="F23" t="n">
-        <v>0.286</v>
+        <v>0.0398</v>
       </c>
       <c r="G23" t="n">
         <v>-3.351</v>
@@ -2248,13 +2248,13 @@
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9389</v>
+        <v>0.3989</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2699</v>
+        <v>-0.0239</v>
       </c>
       <c r="U23" t="n">
-        <v>0.669</v>
+        <v>0.4228</v>
       </c>
       <c r="V23" t="n">
         <v>-0.0005</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.374299999999998</v>
+        <v>-9.3744</v>
       </c>
       <c r="E24" t="n">
-        <v>-13.3759</v>
+        <v>-13.376</v>
       </c>
       <c r="F24" t="n">
-        <v>4.0014</v>
+        <v>4.0015</v>
       </c>
       <c r="G24" t="n">
         <v>-9.8643</v>
@@ -2326,13 +2326,13 @@
         <v>18.5286</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7149</v>
+        <v>-0.7150000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.3842</v>
+        <v>-5.384300000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>4.6692</v>
+        <v>4.6693</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5744</v>
